--- a/resources/reward.xlsx
+++ b/resources/reward.xlsx
@@ -1123,7 +1123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX109"/>
+  <dimension ref="A1:AX107"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col width="16.75" customWidth="1" style="3" min="1" max="1"/>
@@ -5862,102 +5862,84 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="inlineStr">
+      <c r="A99" s="3" t="n">
+        <v>10103</v>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>叛士征讨赏</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="n"/>
+      <c r="D99" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E99" s="3" t="n"/>
+      <c r="F99" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H99" s="0" t="n"/>
+      <c r="I99" s="0" t="n"/>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>(10054,1)</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t>12000</t>
         </is>
       </c>
-      <c r="B99" s="3" t="inlineStr">
+      <c r="B100" s="3" t="inlineStr">
         <is>
           <t>清剿赏金</t>
         </is>
       </c>
-      <c r="C99" s="3" t="n"/>
-      <c r="D99" s="3" t="n"/>
-      <c r="E99" s="3" t="n"/>
-      <c r="F99" s="3" t="inlineStr">
+      <c r="C100" s="3" t="n"/>
+      <c r="D100" s="3" t="n"/>
+      <c r="E100" s="3" t="n"/>
+      <c r="F100" s="3" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="L99" s="3" t="inlineStr">
+      <c r="H100" s="0" t="n"/>
+      <c r="I100" s="0" t="n"/>
+      <c r="L100" s="3" t="inlineStr">
         <is>
           <t>10001</t>
         </is>
       </c>
-      <c r="M99" s="3" t="inlineStr">
+      <c r="M100" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="3" t="n">
-        <v>20010</v>
-      </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>万圣狂欢奖励</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="n"/>
-      <c r="D100" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="E100" s="3" t="n"/>
-      <c r="F100" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="H100" s="0" t="n">
-        <v>80</v>
-      </c>
-      <c r="I100" s="0" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="L100" s="3" t="n">
-        <v>10001</v>
-      </c>
-      <c r="M100" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="N100" s="0" t="n">
-        <v>10005</v>
-      </c>
-      <c r="O100" s="0" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>99001</v>
-      </c>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>测试奖励包</t>
-        </is>
-      </c>
-      <c r="C101" s="3" t="inlineStr">
-        <is>
-          <t>测试奖励包</t>
-        </is>
-      </c>
+        <v>30010</v>
+      </c>
+      <c r="B101" s="3" t="n"/>
+      <c r="C101" s="3" t="n"/>
       <c r="D101" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E101" s="3" t="n"/>
-      <c r="F101" s="3" t="n"/>
+      <c r="F101" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="H101" s="0" t="n"/>
-      <c r="I101" s="0" t="n"/>
-      <c r="L101" s="3" t="n">
-        <v>10001</v>
-      </c>
-      <c r="M101" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="N101" s="0" t="n"/>
-      <c r="O101" s="0" t="n"/>
+      <c r="I101" s="0" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="n"/>
+      <c r="M101" s="3" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
@@ -5994,342 +5976,125 @@
       </c>
       <c r="L102" s="3" t="n"/>
       <c r="M102" s="3" t="n"/>
-      <c r="N102" s="0" t="n"/>
-      <c r="O102" s="0" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
         <v>100601</v>
       </c>
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>测试奖励包</t>
-        </is>
-      </c>
+      <c r="B103" s="3" t="n"/>
       <c r="C103" s="3" t="n"/>
-      <c r="D103" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="D103" s="3" t="n"/>
       <c r="E103" s="3" t="n"/>
       <c r="F103" s="3" t="n"/>
       <c r="H103" s="0" t="n"/>
       <c r="I103" s="0" t="n"/>
-      <c r="L103" s="3" t="inlineStr">
-        <is>
-          <t>(10001,10001,10001,10001,10001)</t>
-        </is>
-      </c>
-      <c r="M103" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="N103" s="0" t="n"/>
-      <c r="O103" s="0" t="n"/>
+      <c r="L103" s="3" t="n"/>
+      <c r="M103" s="3" t="n"/>
+      <c r="AP103" s="0" t="inlineStr">
+        <is>
+          <t>，给两个选项：第一个我这就去讨伐'选完后跳到第二段奖励</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
         <v>100602</v>
       </c>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>测试奖励包</t>
-        </is>
-      </c>
+      <c r="B104" s="3" t="n"/>
       <c r="C104" s="3" t="n"/>
       <c r="D104" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E104" s="3" t="n"/>
-      <c r="F104" s="3" t="n"/>
+      <c r="F104" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="H104" s="0" t="n"/>
-      <c r="I104" s="0" t="n"/>
-      <c r="L104" s="3" t="n">
-        <v>10001</v>
-      </c>
-      <c r="M104" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="N104" s="0" t="n"/>
-      <c r="O104" s="0" t="n"/>
+      <c r="I104" s="0" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="L104" s="3" t="n"/>
+      <c r="M104" s="3" t="n"/>
+      <c r="AP104" s="0" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
         <v>100603</v>
       </c>
-      <c r="B105" s="3" t="inlineStr">
-        <is>
-          <t>测试奖励包</t>
-        </is>
-      </c>
-      <c r="C105" s="3" t="inlineStr">
-        <is>
-          <t>测试奖励包：每日限领1次，必给道具10001×5</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="B105" s="3" t="n"/>
+      <c r="C105" s="3" t="n"/>
+      <c r="D105" s="3" t="n"/>
       <c r="E105" s="3" t="n"/>
-      <c r="F105" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" s="0" t="n"/>
-      <c r="H105" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" s="0" t="n"/>
-      <c r="J105" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K105" s="0" t="n"/>
-      <c r="L105" s="3" t="n">
-        <v>10001</v>
-      </c>
-      <c r="M105" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="N105" s="0" t="n"/>
-      <c r="O105" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="P105" s="0" t="n"/>
-      <c r="Q105" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R105" s="0" t="n"/>
-      <c r="S105" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="T105" s="0" t="n"/>
-      <c r="U105" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="V105" s="0" t="n"/>
-      <c r="W105" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="X105" s="0" t="n"/>
-      <c r="Z105" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA105" s="0" t="n"/>
-      <c r="AC105" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD105" s="0" t="n"/>
-      <c r="AF105" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG105" s="0" t="n"/>
+      <c r="F105" s="3" t="n"/>
+      <c r="H105" s="0" t="n"/>
+      <c r="I105" s="0" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="n"/>
+      <c r="M105" s="3" t="n"/>
+      <c r="AP105" s="0" t="inlineStr">
+        <is>
+          <t>包也建一下</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
         <v>100604</v>
       </c>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>测试奖励包</t>
-        </is>
-      </c>
+      <c r="B106" s="3" t="n"/>
       <c r="C106" s="3" t="n"/>
       <c r="D106" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E106" s="3" t="n"/>
       <c r="F106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G106" s="0" t="n"/>
+        <v>100</v>
+      </c>
       <c r="H106" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" s="0" t="n"/>
-      <c r="J106" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" s="0" t="n"/>
-      <c r="L106" s="3" t="n">
-        <v>10001</v>
+        <v>100</v>
+      </c>
+      <c r="I106" s="0" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>(10070,)</t>
+        </is>
       </c>
       <c r="M106" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="N106" s="0" t="n"/>
-      <c r="O106" s="0" t="n"/>
-      <c r="P106" s="0" t="n"/>
-      <c r="Q106" s="0" t="n"/>
-      <c r="R106" s="0" t="n"/>
-      <c r="S106" s="0" t="n"/>
-      <c r="T106" s="0" t="n"/>
-      <c r="U106" s="0" t="n"/>
-      <c r="V106" s="0" t="n"/>
-      <c r="W106" s="0" t="n"/>
-      <c r="X106" s="0" t="n"/>
-      <c r="Z106" s="0" t="n"/>
-      <c r="AA106" s="0" t="n"/>
-      <c r="AC106" s="0" t="n"/>
-      <c r="AD106" s="0" t="n"/>
-      <c r="AF106" s="0" t="n"/>
-      <c r="AG106" s="0" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="AP106" s="0" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
         <v>100605</v>
       </c>
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>测试奖励包</t>
-        </is>
-      </c>
-      <c r="C107" s="3" t="inlineStr">
-        <is>
-          <t>测试奖励包</t>
-        </is>
-      </c>
+      <c r="B107" s="3" t="n"/>
+      <c r="C107" s="3" t="n"/>
       <c r="D107" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E107" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F107" s="3" t="n"/>
-      <c r="G107" s="0" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="E107" s="3" t="n"/>
+      <c r="F107" s="3" t="n">
+        <v>100</v>
+      </c>
       <c r="H107" s="0" t="n"/>
       <c r="I107" s="0" t="n"/>
-      <c r="J107" s="0" t="n"/>
-      <c r="K107" s="0" t="n"/>
       <c r="L107" s="3" t="n">
-        <v>10001</v>
+        <v>10070</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="N107" s="0" t="n"/>
-      <c r="O107" s="0" t="n"/>
-      <c r="P107" s="0" t="n"/>
-      <c r="Q107" s="0" t="n"/>
-      <c r="R107" s="0" t="n"/>
-      <c r="S107" s="0" t="n"/>
-      <c r="T107" s="0" t="n"/>
-      <c r="U107" s="0" t="n"/>
-      <c r="V107" s="0" t="n"/>
-      <c r="W107" s="0" t="n"/>
-      <c r="X107" s="0" t="n"/>
-      <c r="Z107" s="0" t="n"/>
-      <c r="AA107" s="0" t="n"/>
-      <c r="AC107" s="0" t="n"/>
-      <c r="AD107" s="0" t="n"/>
-      <c r="AF107" s="0" t="n"/>
-      <c r="AG107" s="0" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="3" t="n">
-        <v>100606</v>
-      </c>
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>封魔首通奖励</t>
-        </is>
-      </c>
-      <c r="C108" s="3" t="n"/>
-      <c r="D108" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E108" s="3" t="n"/>
-      <c r="F108" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="G108" s="0" t="n"/>
-      <c r="H108" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="I108" s="0" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J108" s="0" t="n"/>
-      <c r="K108" s="0" t="n"/>
-      <c r="L108" s="3" t="n">
-        <v>10001</v>
-      </c>
-      <c r="M108" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N108" s="0" t="n"/>
-      <c r="O108" s="0" t="n"/>
-      <c r="P108" s="0" t="n"/>
-      <c r="Q108" s="0" t="n"/>
-      <c r="R108" s="0" t="n"/>
-      <c r="S108" s="0" t="n"/>
-      <c r="T108" s="0" t="n"/>
-      <c r="U108" s="0" t="n"/>
-      <c r="V108" s="0" t="n"/>
-      <c r="W108" s="0" t="n"/>
-      <c r="X108" s="0" t="n">
-        <v>2001</v>
-      </c>
-      <c r="Z108" s="0" t="n"/>
-      <c r="AA108" s="0" t="n"/>
-      <c r="AC108" s="0" t="n"/>
-      <c r="AD108" s="0" t="n"/>
-      <c r="AF108" s="0" t="n"/>
-      <c r="AG108" s="0" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="3" t="n">
-        <v>100607</v>
-      </c>
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>封魔首通奖励</t>
-        </is>
-      </c>
-      <c r="C109" s="3" t="inlineStr">
-        <is>
-          <t>封魔首通奖励</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E109" s="3" t="n"/>
-      <c r="F109" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="G109" s="0" t="n"/>
-      <c r="H109" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="I109" s="0" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J109" s="0" t="n"/>
-      <c r="K109" s="0" t="n"/>
-      <c r="L109" s="3" t="n">
-        <v>10001</v>
-      </c>
-      <c r="M109" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N109" s="0" t="n"/>
-      <c r="O109" s="0" t="n"/>
-      <c r="P109" s="0" t="n"/>
-      <c r="Q109" s="0" t="n"/>
-      <c r="R109" s="0" t="n"/>
-      <c r="S109" s="0" t="n"/>
-      <c r="T109" s="0" t="n"/>
-      <c r="U109" s="0" t="n"/>
-      <c r="V109" s="0" t="n"/>
-      <c r="W109" s="0" t="n"/>
-      <c r="X109" s="0" t="n"/>
-      <c r="Z109" s="0" t="n"/>
-      <c r="AA109" s="0" t="n"/>
-      <c r="AC109" s="0" t="n"/>
-      <c r="AD109" s="0" t="n"/>
-      <c r="AF109" s="0" t="n"/>
-      <c r="AG109" s="0" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="AP107" s="0" t="n"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4 A10:A37 A39:A41 A43:A48 A50:A55 A57:A1048576">

--- a/resources/reward.xlsx
+++ b/resources/reward.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="708" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Reward" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reward" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="Z_013C542B_6F19_4C79_B0E1_CF7C44EAF100_.wvu.Cols" localSheetId="1" hidden="1">Reward!#REF!</definedName>
@@ -1123,7 +1123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX100"/>
+  <dimension ref="A1:AX101"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col width="16.75" customWidth="1" style="3" min="1" max="1"/>
@@ -5925,6 +5925,40 @@
         <v>3</v>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="3" t="n">
+        <v>12002</v>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>冰封首通</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="n"/>
+      <c r="D101" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" s="3" t="n"/>
+      <c r="F101" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="H101" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="I101" s="0" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>10070</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="n">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4 A10:A37 A39:A41 A43:A48 A50:A55 A57:A1048576">
     <cfRule type="duplicateValues" priority="1966" dxfId="0"/>

--- a/resources/reward.xlsx
+++ b/resources/reward.xlsx
@@ -1123,7 +1123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX101"/>
+  <dimension ref="A1:AX102"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col width="16.75" customWidth="1" style="3" min="1" max="1"/>
@@ -5959,6 +5959,53 @@
         <v>3</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="3" t="n">
+        <v>12003</v>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>开服七日登录奖</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="n"/>
+      <c r="D102" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" s="3" t="n"/>
+      <c r="F102" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="H102" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="I102" s="0" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N102" s="0" t="inlineStr">
+        <is>
+          <t>10002</t>
+        </is>
+      </c>
+      <c r="O102" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="X102" s="0" t="inlineStr">
+        <is>
+          <t>10003</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4 A10:A37 A39:A41 A43:A48 A50:A55 A57:A1048576">
     <cfRule type="duplicateValues" priority="1966" dxfId="0"/>

--- a/resources/reward.xlsx
+++ b/resources/reward.xlsx
@@ -1123,7 +1123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX100"/>
+  <dimension ref="A1:AX101"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col width="16.75" customWidth="1" style="3" min="1" max="1"/>
@@ -5909,6 +5909,30 @@
         <v>10</v>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="3" t="n">
+        <v>100902</v>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>中秋礼</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="n"/>
+      <c r="D101" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E101" s="3" t="n"/>
+      <c r="F101" s="3" t="n"/>
+      <c r="L101" s="3" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="M101" s="3" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4 A10:A37 A39:A41 A43:A48 A50:A55 A57:A1048576">
     <cfRule type="duplicateValues" priority="1966" dxfId="0"/>

--- a/resources/reward.xlsx
+++ b/resources/reward.xlsx
@@ -1123,7 +1123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX101"/>
+  <dimension ref="A1:AX102"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col width="16.75" customWidth="1" style="3" min="1" max="1"/>
@@ -5863,11 +5863,11 @@
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>100900</v>
+        <v>100831</v>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>中秋礼</t>
+          <t>捣毁巢穴奖励包</t>
         </is>
       </c>
       <c r="C99" s="3" t="n"/>
@@ -5875,19 +5875,28 @@
         <v>1</v>
       </c>
       <c r="E99" s="3" t="n"/>
-      <c r="F99" s="3" t="n"/>
-      <c r="L99" s="3" t="inlineStr">
-        <is>
-          <t>10001</t>
-        </is>
-      </c>
-      <c r="M99" s="3" t="n">
-        <v>10</v>
-      </c>
+      <c r="F99" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G99" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H99" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="0" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L99" s="3" t="n"/>
+      <c r="M99" s="3" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>100901</v>
+        <v>100900</v>
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
@@ -5911,7 +5920,7 @@
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>100902</v>
+        <v>100901</v>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
@@ -5930,6 +5939,33 @@
         </is>
       </c>
       <c r="M101" s="3" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="n">
+        <v>100902</v>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>中秋礼</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="n"/>
+      <c r="D102" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" s="3" t="n"/>
+      <c r="F102" s="3" t="n"/>
+      <c r="G102" s="0" t="n"/>
+      <c r="H102" s="0" t="n"/>
+      <c r="I102" s="0" t="n"/>
+      <c r="L102" s="3" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="M102" s="3" t="n">
         <v>10</v>
       </c>
     </row>

--- a/resources/reward.xlsx
+++ b/resources/reward.xlsx
@@ -1123,7 +1123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX102"/>
+  <dimension ref="A1:AX109"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col width="16.75" customWidth="1" style="3" min="1" max="1"/>
@@ -5863,11 +5863,11 @@
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>100831</v>
+        <v>92002</v>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>捣毁巢穴奖励包</t>
+          <t>试炼头目奖励</t>
         </is>
       </c>
       <c r="C99" s="3" t="n"/>
@@ -5875,24 +5875,23 @@
         <v>1</v>
       </c>
       <c r="E99" s="3" t="n"/>
-      <c r="F99" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="G99" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H99" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" s="0" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L99" s="3" t="n"/>
-      <c r="M99" s="3" t="n"/>
+      <c r="F99" s="3" t="n"/>
+      <c r="L99" s="3" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="M99" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="N99" s="0" t="inlineStr">
+        <is>
+          <t>10003</t>
+        </is>
+      </c>
+      <c r="O99" s="0" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
@@ -5917,14 +5916,16 @@
       <c r="M100" s="3" t="n">
         <v>10</v>
       </c>
+      <c r="N100" s="0" t="n"/>
+      <c r="O100" s="0" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>100901</v>
+        <v>900001</v>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>中秋礼</t>
+          <t>赤焰进化奖励</t>
         </is>
       </c>
       <c r="C101" s="3" t="n"/>
@@ -5939,16 +5940,18 @@
         </is>
       </c>
       <c r="M101" s="3" t="n">
-        <v>10</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="N101" s="0" t="n"/>
+      <c r="O101" s="0" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>100902</v>
+        <v>910003</v>
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>中秋礼</t>
+          <t>试炼第三天奖励</t>
         </is>
       </c>
       <c r="C102" s="3" t="n"/>
@@ -5957,16 +5960,201 @@
       </c>
       <c r="E102" s="3" t="n"/>
       <c r="F102" s="3" t="n"/>
-      <c r="G102" s="0" t="n"/>
-      <c r="H102" s="0" t="n"/>
-      <c r="I102" s="0" t="n"/>
       <c r="L102" s="3" t="inlineStr">
         <is>
           <t>10001</t>
         </is>
       </c>
       <c r="M102" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="N102" s="0" t="inlineStr">
+        <is>
+          <t>10003</t>
+        </is>
+      </c>
+      <c r="O102" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="n">
+        <v>910007</v>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>试炼第七天奖励</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="n"/>
+      <c r="D103" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E103" s="3" t="n"/>
+      <c r="F103" s="3" t="n"/>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="N103" s="0" t="inlineStr">
+        <is>
+          <t>10003</t>
+        </is>
+      </c>
+      <c r="O103" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="n">
+        <v>910008</v>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>赤焰进化奖励</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="n"/>
+      <c r="D104" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" s="3" t="n"/>
+      <c r="F104" s="3" t="n"/>
+      <c r="L104" s="3" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="M104" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="N104" s="0" t="n"/>
+      <c r="O104" s="0" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="n">
+        <v>910009</v>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>中秋礼</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="n"/>
+      <c r="D105" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E105" s="3" t="n"/>
+      <c r="F105" s="3" t="n"/>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="n">
         <v>10</v>
+      </c>
+      <c r="N105" s="0" t="n"/>
+      <c r="O105" s="0" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="n">
+        <v>910010</v>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>中秋礼</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="n"/>
+      <c r="D106" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" s="3" t="n"/>
+      <c r="F106" s="3" t="n"/>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>10001</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N106" s="0" t="n"/>
+      <c r="O106" s="0" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="n">
+        <v>910011</v>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>新手礼包</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="n"/>
+      <c r="D107" s="3" t="n"/>
+      <c r="E107" s="3" t="n"/>
+      <c r="F107" s="3" t="n"/>
+      <c r="L107" s="3" t="n"/>
+      <c r="M107" s="3" t="n"/>
+      <c r="N107" s="0" t="n"/>
+      <c r="O107" s="0" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="n">
+        <v>910012</v>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>中秋礼</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="n"/>
+      <c r="D108" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E108" s="3" t="n"/>
+      <c r="F108" s="3" t="n"/>
+      <c r="L108" s="3" t="n"/>
+      <c r="M108" s="3" t="n"/>
+      <c r="N108" s="0" t="n"/>
+      <c r="O108" s="0" t="n"/>
+      <c r="AP108" s="0" t="inlineStr">
+        <is>
+          <t>10001×10</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="n">
+        <v>910013</v>
+      </c>
+      <c r="B109" s="3" t="n">
+        <v>910012</v>
+      </c>
+      <c r="C109" s="3" t="n"/>
+      <c r="D109" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" s="3" t="n"/>
+      <c r="F109" s="3" t="n"/>
+      <c r="L109" s="3" t="inlineStr">
+        <is>
+          <t>10001×10</t>
+        </is>
+      </c>
+      <c r="M109" s="3" t="n"/>
+      <c r="N109" s="0" t="n"/>
+      <c r="O109" s="0" t="n"/>
+      <c r="AP109" s="0" t="inlineStr">
+        <is>
+          <t>10001×10</t>
+        </is>
       </c>
     </row>
   </sheetData>
